--- a/data/export/2026-10-23-operations.xlsx
+++ b/data/export/2026-10-23-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1583,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1720,7 +1752,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1836,7 +1868,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1952,7 +1984,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2416,7 +2456,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2506,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2519,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2567,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2586,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2622,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,49 +2650,45 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2712,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2732,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2767,12 +2799,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2883,12 +2915,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2970,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3031,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3050,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3086,3603 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-operations.xlsx
+++ b/data/export/2026-10-23-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,14 +1215,14 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -1222,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1686,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2425,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2572,7 +2616,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2688,7 +2736,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3036,7 +3092,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,46 +3251,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3327,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,7 +3371,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3318,35 +3382,35 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3443,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3462,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,18 +3487,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3447,60 +3515,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,33 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3563,60 +3639,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3763,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3815,40 +3907,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3872,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3911,7 +4011,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +4021,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3931,12 +4031,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4059,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4072,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4143,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4143,22 +4259,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4191,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4259,22 +4375,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4307,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4491,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4423,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4607,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4539,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4710,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4607,22 +4723,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4655,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4826,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4839,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4733,7 +4849,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4771,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4942,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5047,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5058,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5119,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5174,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5290,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5638,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5754,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5870,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5820,7 +5936,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5986,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6047,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6066,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6102,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6163,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6182,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6218,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6163,12 +6279,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6298,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6334,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6395,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6414,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6450,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6511,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6530,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6566,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6511,12 +6627,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6646,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6566,35 +6682,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6627,12 +6743,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6762,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6676,13 +6792,3217 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC53" s="2" t="inlineStr"/>
-      <c r="AD53" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-operations.xlsx
+++ b/data/export/2026-10-23-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1991,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,37 +2052,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2148,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2376,7 +2380,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2430,7 +2434,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2500,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2616,7 +2620,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2670,7 +2674,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2740,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2790,7 +2794,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2860,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +2976,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3092,7 +3096,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3146,7 +3150,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3216,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3332,7 +3336,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3448,7 +3452,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3497,7 +3501,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3509,62 +3513,58 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,37 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3639,24 +3639,24 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3669,19 +3669,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3763,24 +3763,24 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:26</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3793,24 +3793,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3859,22 +3859,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3887,24 +3887,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4011,52 +4011,56 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4064,7 +4068,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4072,29 +4076,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq30（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4104,33 +4092,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4135,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4153,7 +4145,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4163,12 +4155,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq42，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4191,12 +4183,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4204,13 +4196,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4259,22 +4267,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4307,12 +4315,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4334,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4375,22 +4383,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4423,12 +4431,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4450,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4491,22 +4499,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4539,12 +4547,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4607,22 +4615,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4655,12 +4663,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4682,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4723,22 +4731,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4776,7 +4784,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4839,7 +4847,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4849,7 +4857,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4887,12 +4895,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4914,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4955,22 +4963,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5022,7 +5030,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5071,22 +5079,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5119,12 +5127,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5187,22 +5195,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5240,7 +5248,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5262,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5303,22 +5311,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5351,12 +5359,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5419,22 +5427,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5467,12 +5475,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5494,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5535,22 +5543,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5583,12 +5591,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5651,22 +5659,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5704,7 +5712,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5726,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5767,22 +5775,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5820,7 +5828,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5883,22 +5891,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5931,12 +5939,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5950,7 +5958,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5999,22 +6007,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6047,12 +6055,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6115,7 +6123,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6125,7 +6133,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6163,12 +6171,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6190,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,22 +6239,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6279,12 +6287,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6347,7 +6355,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6365,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6400,7 +6408,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6422,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6516,7 +6524,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6579,22 +6587,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6627,12 +6635,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6646,7 +6654,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6695,22 +6703,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6743,12 +6751,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6762,7 +6770,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6787,22 +6795,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6815,22 +6819,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6868,7 +6872,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6882,7 +6886,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6917,12 +6921,12 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -6935,22 +6939,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6988,7 +6992,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7002,7 +7006,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7037,82 +7041,78 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7136,17 +7136,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7209,24 +7209,24 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7250,7 +7250,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7323,32 +7323,36 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7356,7 +7360,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7370,7 +7374,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7380,17 +7384,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7400,13 +7404,17 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7419,24 +7427,24 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7449,34 +7457,34 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7525,12 +7533,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7551,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7553,7 +7561,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7573,12 +7581,12 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
@@ -7600,7 +7608,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7614,7 +7622,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7649,12 +7657,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7667,60 +7675,64 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7744,33 +7756,37 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7799,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7793,7 +7809,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7803,40 +7819,44 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7850,7 +7870,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7860,33 +7880,37 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7899,56 +7923,52 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7980,37 +8000,33 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8023,60 +8039,64 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8090,7 +8110,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8100,33 +8120,37 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8139,22 +8163,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8192,7 +8216,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8206,7 +8230,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8231,7 +8255,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8255,52 +8279,56 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8308,7 +8336,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8322,7 +8350,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8332,33 +8360,37 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8371,22 +8403,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8424,7 +8456,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8438,7 +8470,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8487,22 +8519,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8535,12 +8567,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8603,7 +8635,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8613,7 +8645,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8651,12 +8683,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8670,7 +8702,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8719,22 +8751,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8767,12 +8799,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8786,7 +8818,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8835,22 +8867,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8883,12 +8915,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8902,7 +8934,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8951,22 +8983,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>07:59</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8999,12 +9031,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9018,7 +9050,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9043,22 +9075,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9071,22 +9099,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9119,12 +9147,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9138,7 +9166,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9163,18 +9191,22 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9187,22 +9219,22 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -9235,12 +9267,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9254,7 +9286,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9279,22 +9311,18 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9307,22 +9335,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9355,12 +9383,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9374,7 +9402,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9409,12 +9437,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9427,22 +9455,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9475,12 +9503,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9494,7 +9522,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9519,18 +9547,22 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9543,22 +9575,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9591,12 +9623,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9610,7 +9642,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9635,22 +9667,18 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9663,22 +9691,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9711,12 +9739,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9730,7 +9758,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9760,13 +9788,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9779,22 +9811,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9827,12 +9859,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9846,7 +9878,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9881,12 +9913,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9899,22 +9931,22 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9947,12 +9979,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9966,43 +9998,287 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="X82" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA82" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-operations.xlsx
+++ b/data/export/2026-10-23-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD82"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1761,24 +1761,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>99分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1875,32 +1875,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1932,33 +1936,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2001,24 +2009,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2028,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2077,12 +2085,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2115,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2148,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2172,33 +2184,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2231,32 +2247,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2264,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2288,33 +2308,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2347,32 +2371,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2380,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2404,37 +2432,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2467,32 +2495,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2500,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2524,17 +2556,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2544,17 +2576,17 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2652,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2659,7 +2691,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2740,7 +2772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2794,7 +2826,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2892,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2976,7 +3008,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3030,7 +3062,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3128,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3216,7 +3248,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3270,7 +3302,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3368,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,7 +3484,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3501,12 +3533,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3519,22 +3551,22 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3572,7 +3604,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3618,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3611,84 +3643,80 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3696,7 +3724,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3748,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,17 +3868,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3869,82 +3893,78 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3968,99 +3988,95 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4068,7 +4084,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4082,7 +4098,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4092,75 +4108,75 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq42，推进13站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4188,7 +4204,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4196,29 +4212,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>物理seq30（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4243,18 +4243,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4271,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4277,7 +4281,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4287,40 +4291,44 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4334,7 +4342,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4344,33 +4352,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4395,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4393,7 +4405,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4403,32 +4415,36 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4436,7 +4452,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4450,7 +4466,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4460,33 +4476,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4519,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4509,7 +4529,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4519,40 +4539,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4566,7 +4590,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4576,33 +4600,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4643,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4625,7 +4653,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4635,40 +4663,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4682,7 +4714,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4692,33 +4724,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4767,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4741,7 +4777,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4751,12 +4787,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4779,12 +4815,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4792,13 +4828,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4823,7 +4875,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4847,60 +4899,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4914,7 +4970,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4924,33 +4980,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4963,7 +5023,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4973,7 +5033,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5011,12 +5071,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5030,7 +5090,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5055,7 +5115,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5079,7 +5139,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5089,7 +5149,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5099,40 +5159,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5146,7 +5210,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5156,33 +5220,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5263,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5205,7 +5273,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5243,12 +5311,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5262,7 +5330,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5287,7 +5355,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5311,7 +5379,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5321,7 +5389,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5359,12 +5427,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5378,7 +5446,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5403,7 +5471,7 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5427,7 +5495,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5437,7 +5505,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5475,12 +5543,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5494,7 +5562,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5543,32 +5611,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5591,12 +5659,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5604,13 +5672,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5659,22 +5743,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5707,12 +5791,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5726,7 +5810,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5775,22 +5859,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5823,12 +5907,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5842,7 +5926,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5891,22 +5975,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5939,12 +6023,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5958,7 +6042,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6007,22 +6091,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6055,12 +6139,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6074,7 +6158,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6123,22 +6207,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6171,12 +6255,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6190,7 +6274,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6239,7 +6323,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A62773D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6249,7 +6333,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6287,12 +6371,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6306,7 +6390,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6355,7 +6439,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6365,7 +6449,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6403,12 +6487,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6422,7 +6506,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6471,7 +6555,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6481,7 +6565,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6519,12 +6603,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6538,7 +6622,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6587,7 +6671,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6597,7 +6681,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6635,12 +6719,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6654,7 +6738,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6703,7 +6787,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6713,7 +6797,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6751,12 +6835,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6770,7 +6854,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6819,22 +6903,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62773D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6867,12 +6951,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6886,7 +6970,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6911,22 +6995,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6939,22 +7019,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6992,7 +7072,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7006,7 +7086,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7031,22 +7111,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7059,22 +7135,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7112,7 +7188,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7126,7 +7202,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7151,92 +7227,84 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7250,7 +7318,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7260,107 +7328,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>07:53</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7374,7 +7434,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7384,107 +7444,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7498,7 +7550,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7508,17 +7560,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7533,82 +7585,78 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7622,7 +7670,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7632,17 +7680,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7657,82 +7705,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7746,7 +7790,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7756,17 +7800,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7781,82 +7825,78 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7870,7 +7910,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7880,17 +7920,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7905,40 +7945,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7971,12 +8011,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7990,7 +8030,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8015,7 +8055,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -8026,77 +8066,73 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8110,7 +8146,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8120,17 +8156,17 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8145,40 +8181,40 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8211,12 +8247,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8230,7 +8266,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8255,7 +8291,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8266,77 +8302,73 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8350,7 +8382,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8360,17 +8392,17 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8385,40 +8417,40 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8451,12 +8483,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8470,7 +8502,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8495,7 +8527,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8506,35 +8538,35 @@
       <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8567,12 +8599,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8586,7 +8618,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8611,7 +8643,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8622,7 +8654,7 @@
       <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -8635,7 +8667,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8645,7 +8677,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8655,40 +8687,44 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8702,7 +8738,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8712,33 +8748,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8791,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8761,7 +8801,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8771,40 +8811,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8818,7 +8862,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8828,33 +8872,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8867,52 +8915,56 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8920,7 +8972,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8934,7 +8986,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8944,33 +8996,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8983,60 +9039,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9050,7 +9110,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9060,33 +9120,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9163,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9109,7 +9173,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9119,40 +9183,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9166,7 +9234,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9176,17 +9244,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9201,12 +9269,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9287,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9229,7 +9297,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9239,40 +9307,44 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9286,7 +9358,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9296,33 +9368,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9335,60 +9411,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9402,7 +9482,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9412,17 +9492,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9437,12 +9517,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9455,52 +9535,56 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9508,7 +9592,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9522,7 +9606,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9532,17 +9616,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9557,12 +9641,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9575,60 +9659,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9642,7 +9730,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9652,33 +9740,37 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9691,60 +9783,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9758,7 +9854,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9768,17 +9864,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9793,7 +9889,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -9811,60 +9907,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9878,7 +9978,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9888,17 +9988,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9913,12 +10013,12 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9931,7 +10031,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9941,7 +10041,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9951,40 +10051,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9998,7 +10102,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10008,17 +10112,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10033,12 +10137,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10051,7 +10155,7 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -10061,7 +10165,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -10071,40 +10175,44 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10118,7 +10226,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10128,17 +10236,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10153,12 +10261,12 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10171,7 +10279,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10181,7 +10289,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10219,12 +10327,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10238,47 +10346,2675 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:59</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
-      <c r="AD82" s="2" t="inlineStr">
-        <is>
-          <t>6/18</t>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-23-operations.xlsx
+++ b/data/export/2026-10-23-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD309"/>
+  <dimension ref="A1:AD310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2208,17 +2208,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2456,17 +2456,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3820,17 +3820,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3944,17 +3944,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4192,17 +4192,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5180,17 +5180,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5304,17 +5304,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5552,17 +5552,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,17 +6420,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7284,17 +7284,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7900,17 +7900,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8272,17 +8272,17 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8636,17 +8636,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8760,17 +8760,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9204,7 +9204,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9248,17 +9248,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10236,17 +10236,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10360,17 +10360,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10728,17 +10728,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10976,17 +10976,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11401,24 +11401,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11525,24 +11525,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11639,32 +11639,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11672,7 +11676,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11696,17 +11700,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11716,17 +11720,17 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -11759,32 +11763,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11792,7 +11800,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11816,17 +11824,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11836,17 +11844,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11879,32 +11887,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11912,7 +11924,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11936,17 +11948,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11956,17 +11968,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11999,32 +12011,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12032,7 +12048,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12056,17 +12072,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12076,17 +12092,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12125,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -12152,7 +12168,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12166,7 +12182,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -12206,7 +12222,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12288,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12321,12 +12337,12 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12408,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12436,17 +12452,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12532,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12694,7 +12710,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12834,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12958,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13160,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13198,7 +13214,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -13264,7 +13280,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13442,7 +13458,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -13628,7 +13644,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13682,7 +13698,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13768,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13806,7 +13822,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14148,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14176,17 +14192,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -14252,7 +14268,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14306,7 +14322,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -14376,7 +14392,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14420,12 +14436,12 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
@@ -14554,7 +14570,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14636,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14664,17 +14680,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14760,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14798,7 +14814,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14868,7 +14884,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14922,7 +14938,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15128,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15232,7 +15248,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15476,7 +15492,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15520,13 +15536,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC122" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC122" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -15720,7 +15740,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15894,7 +15914,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15984,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16142,7 +16162,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16286,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16488,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16522,7 +16542,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16612,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16770,7 +16790,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -16964,7 +16984,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17018,7 +17038,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17108,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17142,7 +17162,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17232,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17256,17 +17276,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17480,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17504,12 +17524,12 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
@@ -17584,7 +17604,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17638,7 +17658,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -17708,7 +17728,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17752,17 +17772,17 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17906,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -17952,7 +17972,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18006,7 +18026,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -18076,7 +18096,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18130,7 +18150,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18344,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18572,7 +18592,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18750,7 +18770,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -18874,7 +18894,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -19122,7 +19142,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -19188,7 +19208,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19568,7 +19588,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19742,7 +19762,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -19812,7 +19832,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19856,12 +19876,12 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -20060,7 +20080,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20114,7 +20134,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20486,7 +20506,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20606,7 +20626,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -20800,7 +20820,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -21180,7 +21200,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21234,7 +21254,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21300,7 +21320,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21420,7 +21440,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21540,7 +21560,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21584,13 +21604,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC171" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC171" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -21656,7 +21680,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21700,17 +21724,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -21776,7 +21800,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21896,7 +21920,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21940,17 +21964,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -22016,7 +22040,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22136,7 +22160,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22260,7 +22284,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22314,7 +22338,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22408,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22508,7 +22532,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22562,7 +22586,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22686,7 +22710,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22810,7 +22834,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23004,7 +23028,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23058,7 +23082,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23330,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23450,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -23492,7 +23516,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23856,7 +23880,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23910,7 +23934,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -23976,7 +24000,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24063,32 +24087,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -24096,7 +24124,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24120,17 +24148,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24140,12 +24168,12 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
@@ -24183,32 +24211,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -24216,7 +24248,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24240,17 +24272,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24260,13 +24292,17 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC193" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC193" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -24332,7 +24368,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24386,7 +24422,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -24419,12 +24455,12 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq29推进至seq50，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -24452,7 +24488,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24539,32 +24575,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -24572,7 +24612,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24596,17 +24636,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24616,17 +24656,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -24659,12 +24699,12 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程37%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
@@ -24692,7 +24732,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24700,10 +24740,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R197" s="2" t="inlineStr"/>
-      <c r="S197" s="2" t="inlineStr"/>
+      <c r="R197" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S197" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
       <c r="T197" s="2" t="inlineStr"/>
-      <c r="U197" s="2" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V197" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24812,7 +24864,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24928,7 +24980,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25015,32 +25067,36 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -25048,7 +25104,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25072,17 +25128,17 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA200" s="2" t="inlineStr">
@@ -25092,17 +25148,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25168,7 +25224,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25222,7 +25278,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25344,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25342,7 +25398,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -25408,7 +25464,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25462,7 +25518,7 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -25528,7 +25584,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25582,7 +25638,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -25648,7 +25704,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25702,7 +25758,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -25772,7 +25828,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25816,17 +25872,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -25950,7 +26006,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26268,7 +26324,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26312,17 +26368,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26392,7 +26448,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26436,17 +26492,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26570,7 +26626,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26764,7 +26820,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26808,17 +26864,17 @@
       </c>
       <c r="AB214" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26888,7 +26944,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -26932,17 +26988,17 @@
       </c>
       <c r="AB215" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC215" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27370,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27434,7 +27490,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27624,7 +27680,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27663,17 +27719,17 @@
       </c>
       <c r="AA221" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
@@ -27748,7 +27804,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27792,17 +27848,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -27868,7 +27924,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27917,12 +27973,12 @@
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28046,7 +28102,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28360,7 +28416,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28404,17 +28460,17 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28608,7 +28664,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28652,17 +28708,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28906,7 +28962,7 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28976,7 +29032,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29020,17 +29076,17 @@
       </c>
       <c r="AB232" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC232" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29100,7 +29156,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29144,17 +29200,17 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29702,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29716,7 +29772,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29755,17 +29811,17 @@
       </c>
       <c r="AA238" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
@@ -29894,7 +29950,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30140,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30140,17 +30196,17 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -30522,7 +30578,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30588,7 +30644,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30632,17 +30688,17 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31134,7 +31190,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31258,7 +31314,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31750,7 +31806,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32242,7 +32298,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32366,7 +32422,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32680,7 +32736,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32724,17 +32780,17 @@
       </c>
       <c r="AB262" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32982,7 +33038,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33410,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33424,7 +33480,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33468,17 +33524,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33668,7 +33724,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q270" s="2" t="inlineStr">
@@ -33712,17 +33768,17 @@
       </c>
       <c r="AB270" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC270" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33792,7 +33848,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33841,12 +33897,12 @@
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33970,7 +34026,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34040,7 +34096,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q273" s="2" t="inlineStr">
@@ -34084,17 +34140,17 @@
       </c>
       <c r="AB273" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC273" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34218,7 +34274,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34288,7 +34344,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34327,17 +34383,17 @@
       </c>
       <c r="AA275" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34536,7 +34592,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34580,17 +34636,17 @@
       </c>
       <c r="AB277" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34908,7 +34964,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -34952,17 +35008,17 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35206,7 +35262,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35450,7 +35506,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35520,7 +35576,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35564,17 +35620,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35764,7 +35820,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35808,17 +35864,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35884,7 +35940,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35933,12 +35989,12 @@
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36058,7 +36114,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36124,7 +36180,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36168,17 +36224,17 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36248,7 +36304,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36287,17 +36343,17 @@
       </c>
       <c r="AA291" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB291" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
@@ -36426,7 +36482,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36744,7 +36800,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36788,17 +36844,17 @@
       </c>
       <c r="AB295" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC295" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37112,7 +37168,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37156,17 +37212,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37290,7 +37346,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37457,24 +37513,24 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -37484,7 +37540,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37533,12 +37589,12 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -37581,24 +37637,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37608,7 +37664,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37652,17 +37708,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37695,32 +37751,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -37728,7 +37788,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37752,17 +37812,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37772,17 +37832,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37815,32 +37875,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -37848,7 +37912,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37872,17 +37936,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37892,17 +37956,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37935,32 +37999,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -37968,7 +38036,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -37992,17 +38060,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38012,17 +38080,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -38055,32 +38123,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -38088,7 +38160,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38112,32 +38184,32 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
@@ -38175,32 +38247,36 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O307" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -38208,7 +38284,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38232,17 +38308,17 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA307" s="2" t="inlineStr">
@@ -38252,17 +38328,17 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -38295,32 +38371,36 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
       <c r="L308" s="2" t="inlineStr"/>
       <c r="M308" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N308" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N308" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O308" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -38328,7 +38408,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38352,17 +38432,17 @@
       </c>
       <c r="X308" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y308" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z308" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA308" s="2" t="inlineStr">
@@ -38372,17 +38452,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -38448,7 +38528,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q309" s="2" t="inlineStr">
@@ -38492,17 +38572,137 @@
       </c>
       <c r="AB309" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC309" s="2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD309" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr"/>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr"/>
+      <c r="M310" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N310" s="2" t="inlineStr"/>
+      <c r="O310" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P310" s="2" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R310" s="2" t="inlineStr"/>
+      <c r="S310" s="2" t="inlineStr"/>
+      <c r="T310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="W310" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X310" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y310" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z310" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA310" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB310" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC310" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD310" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
         </is>
       </c>
     </row>
